--- a/MC_simulation/MC_simulation_types/ForSimulation_Adults.xlsx
+++ b/MC_simulation/MC_simulation_types/ForSimulation_Adults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Current_work\Linguistics\Gradience\Experiments_final\2_Adults_3syll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthi2revithiadou/Desktop/Supplemental_materials/MC_simulation/MC_simulation_types/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BC0928-EF50-4A87-8ECE-DA869C54AB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1639805-D3B4-DC4E-AD34-F95973A4DBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="660" windowWidth="28160" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -460,15 +460,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -508,7 +508,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -528,7 +528,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -548,7 +548,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -568,7 +568,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -588,7 +588,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -608,7 +608,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -616,7 +616,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="D8" s="1">
         <v>4.5502645502645503E-2</v>
@@ -628,7 +628,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -648,7 +648,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -669,7 +669,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -690,7 +690,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -710,7 +710,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -730,7 +730,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -750,7 +750,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -778,13 +778,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -795,7 +795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0.2</v>
       </c>
